--- a/originales/respuestas/2025/01. Calificadas/root/Subred Integrada De Servicios De Salud Sur Occidente.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Subred Integrada De Servicios De Salud Sur Occidente.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="163">
   <si>
     <t>Entidad</t>
   </si>
@@ -206,9 +206,6 @@
   </si>
   <si>
     <t>Total de colaboradores para 2024.</t>
-  </si>
-  <si>
-    <t>4,48</t>
   </si>
   <si>
     <t>Pregunta 10.</t>
@@ -404,7 +401,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -413,7 +410,7 @@
     <t>Espacios de ideación y cocreación con los equipos internos., Incentivos o reconocimientos a iniciativas innovadoras de los funcionarios., Procesos de formación o capacitaciones en metodologías de innovación.</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -531,7 +528,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -554,6 +551,15 @@
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
@@ -648,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -709,16 +715,29 @@
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2189,11 +2208,17 @@
         <v>5.88697E16</v>
       </c>
       <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
+      <c r="K4" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="M4" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
+      <c r="O4" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
@@ -2240,11 +2265,17 @@
         <v>6.15322E16</v>
       </c>
       <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
+      <c r="K5" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="M5" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
+      <c r="O5" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
@@ -2338,11 +2369,17 @@
         <v>8.1848863669E10</v>
       </c>
       <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="K7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="M7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
+      <c r="O7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P7" s="10"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
@@ -2389,11 +2426,17 @@
         <v>3.930114032E10</v>
       </c>
       <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+      <c r="K8" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
+      <c r="M8" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
+      <c r="O8" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P8" s="10"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
@@ -2485,11 +2528,17 @@
         <v>1.251458283E9</v>
       </c>
       <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="K10" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="M10" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
+      <c r="O10" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
@@ -2638,11 +2687,17 @@
         <v>1.761625335E9</v>
       </c>
       <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="K13" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
+      <c r="M13" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
+      <c r="O13" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2734,11 +2789,17 @@
         <v>1089.0</v>
       </c>
       <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="K15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
+      <c r="M15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
+      <c r="O15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
@@ -2785,11 +2846,17 @@
         <v>1037.0</v>
       </c>
       <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="K16" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+      <c r="M16" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
+      <c r="O16" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
@@ -2836,11 +2903,17 @@
         <v>11.0</v>
       </c>
       <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="K17" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
+      <c r="M17" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
+      <c r="O17" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
@@ -2887,11 +2960,17 @@
         <v>11.0</v>
       </c>
       <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+      <c r="K18" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
+      <c r="M18" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
+      <c r="O18" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P18" s="10"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
@@ -2989,11 +3068,17 @@
         <v>5258.0</v>
       </c>
       <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
+      <c r="K20" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="M20" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
+      <c r="O20" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
@@ -3036,15 +3121,21 @@
       <c r="H21" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="10" t="s">
-        <v>62</v>
+      <c r="I21" s="12">
+        <v>4.48</v>
       </c>
       <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
+      <c r="K21" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
+      <c r="M21" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
+      <c r="O21" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P21" s="10"/>
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
@@ -3073,7 +3164,7 @@
         <v>26.0</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>51</v>
@@ -3082,7 +3173,7 @@
         <v>22</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>33</v>
@@ -3091,11 +3182,17 @@
         <v>208.0</v>
       </c>
       <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
+      <c r="K22" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="M22" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
+      <c r="O22" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -3124,7 +3221,7 @@
         <v>27.0</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>51</v>
@@ -3133,7 +3230,7 @@
         <v>22</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>33</v>
@@ -3142,11 +3239,17 @@
         <v>208.0</v>
       </c>
       <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
+      <c r="K23" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="M23" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
+      <c r="O23" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
@@ -3175,7 +3278,7 @@
         <v>28.0</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>51</v>
@@ -3184,13 +3287,13 @@
         <v>22</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>45</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
@@ -3226,16 +3329,16 @@
         <v>29.0</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>24</v>
@@ -3285,16 +3388,16 @@
         <v>30.0</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>24</v>
@@ -3344,16 +3447,16 @@
         <v>31.0</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>24</v>
@@ -3393,22 +3496,22 @@
         <v>32.0</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>45</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
@@ -4425,7 +4528,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="31" width="10.71"/>
+    <col customWidth="1" min="1" max="8" width="10.71"/>
+    <col customWidth="1" min="9" max="9" width="42.43"/>
+    <col customWidth="1" min="10" max="31" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
@@ -4436,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
@@ -4510,19 +4615,19 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>25</v>
@@ -4557,19 +4662,19 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="H3" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>25</v>
@@ -4604,19 +4709,19 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>85</v>
-      </c>
       <c r="H4" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>25</v>
@@ -4651,19 +4756,19 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>87</v>
-      </c>
       <c r="H5" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>25</v>
@@ -4700,19 +4805,19 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>89</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>25</v>
@@ -4749,33 +4854,43 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>92</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>45</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="K7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L7" s="15"/>
-      <c r="M7" s="10"/>
+      <c r="M7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
+      <c r="O7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
+      <c r="Q7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="R7" s="10"/>
-      <c r="S7" s="16"/>
+      <c r="S7" s="19">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="8" ht="126.75" customHeight="1">
       <c r="A8" s="6" t="s">
@@ -4788,33 +4903,43 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="18"/>
+      <c r="K8" s="20">
+        <v>4.0</v>
+      </c>
+      <c r="L8" s="21"/>
+      <c r="M8" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="N8" s="21"/>
+      <c r="O8" s="20">
+        <v>4.0</v>
+      </c>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="R8" s="21"/>
+      <c r="S8" s="23">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="9" ht="126.75" customHeight="1">
       <c r="A9" s="6" t="s">
@@ -4827,33 +4952,43 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="18"/>
+      <c r="K9" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="L9" s="21"/>
+      <c r="M9" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="N9" s="21"/>
+      <c r="O9" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="R9" s="21"/>
+      <c r="S9" s="23">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="10" ht="126.75" customHeight="1">
       <c r="A10" s="10" t="s">
@@ -4866,33 +5001,43 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>101</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>45</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
+      <c r="K10" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L10" s="15"/>
-      <c r="M10" s="10"/>
+      <c r="M10" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
+      <c r="O10" s="12">
+        <v>4.0</v>
+      </c>
       <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
+      <c r="Q10" s="12">
+        <v>3.0</v>
+      </c>
       <c r="R10" s="10"/>
-      <c r="S10" s="16"/>
+      <c r="S10" s="19">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="11" ht="126.75" customHeight="1">
       <c r="A11" s="6" t="s">
@@ -4905,33 +5050,43 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L11" s="17"/>
-      <c r="M11" s="6"/>
+      <c r="M11" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
+      <c r="O11" s="8">
+        <v>2.0</v>
+      </c>
       <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
+      <c r="Q11" s="8">
+        <v>3.0</v>
+      </c>
       <c r="R11" s="6"/>
-      <c r="S11" s="18"/>
+      <c r="S11" s="24">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="12" ht="126.75" customHeight="1">
       <c r="A12" s="6" t="s">
@@ -4944,33 +5099,43 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="8">
+        <v>4.0</v>
+      </c>
       <c r="L12" s="17"/>
-      <c r="M12" s="6"/>
+      <c r="M12" s="8">
+        <v>4.0</v>
+      </c>
       <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
+      <c r="O12" s="8">
+        <v>4.0</v>
+      </c>
       <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
+      <c r="Q12" s="8">
+        <v>3.0</v>
+      </c>
       <c r="R12" s="6"/>
-      <c r="S12" s="18"/>
+      <c r="S12" s="24">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="13" ht="126.75" customHeight="1">
       <c r="A13" s="10" t="s">
@@ -4983,33 +5148,43 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>45</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="K13" s="12">
+        <v>4.0</v>
+      </c>
       <c r="L13" s="15"/>
-      <c r="M13" s="10"/>
+      <c r="M13" s="12">
+        <v>4.0</v>
+      </c>
       <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
+      <c r="O13" s="12">
+        <v>4.0</v>
+      </c>
       <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
+      <c r="Q13" s="12">
+        <v>4.0</v>
+      </c>
       <c r="R13" s="10"/>
-      <c r="S13" s="16"/>
+      <c r="S13" s="19">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="14" ht="126.75" customHeight="1">
       <c r="A14" s="10" t="s">
@@ -5022,33 +5197,43 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>45</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="K14" s="12">
+        <v>4.0</v>
+      </c>
       <c r="L14" s="15"/>
-      <c r="M14" s="10"/>
+      <c r="M14" s="12">
+        <v>4.0</v>
+      </c>
       <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
+      <c r="O14" s="12">
+        <v>4.0</v>
+      </c>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12">
+        <v>4.0</v>
+      </c>
       <c r="R14" s="10"/>
-      <c r="S14" s="16"/>
+      <c r="S14" s="19">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="15" ht="126.75" customHeight="1">
       <c r="A15" s="10" t="s">
@@ -5061,33 +5246,43 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>45</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="K15" s="12">
+        <v>2.0</v>
+      </c>
       <c r="L15" s="15"/>
-      <c r="M15" s="10"/>
+      <c r="M15" s="12">
+        <v>2.0</v>
+      </c>
       <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
+      <c r="O15" s="12">
+        <v>1.0</v>
+      </c>
       <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
+      <c r="Q15" s="12">
+        <v>2.0</v>
+      </c>
       <c r="R15" s="10"/>
-      <c r="S15" s="16"/>
+      <c r="S15" s="19">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="16" ht="126.75" customHeight="1">
       <c r="A16" s="10" t="s">
@@ -5100,19 +5295,19 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="F16" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="H16" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>25</v>
@@ -5147,19 +5342,19 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>123</v>
-      </c>
       <c r="H17" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>25</v>
@@ -5191,30 +5386,40 @@
       <c r="C18" s="7">
         <v>17.0</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>124</v>
+      <c r="D18" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="8">
+        <v>4.0</v>
+      </c>
       <c r="L18" s="17"/>
-      <c r="M18" s="6"/>
+      <c r="M18" s="8">
+        <v>4.0</v>
+      </c>
       <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
+      <c r="O18" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
+      <c r="Q18" s="8">
+        <v>4.0</v>
+      </c>
       <c r="R18" s="6"/>
-      <c r="S18" s="18"/>
+      <c r="S18" s="24">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="19" ht="126.75" customHeight="1">
       <c r="A19" s="10" t="s">
@@ -5224,30 +5429,40 @@
       <c r="C19" s="11">
         <v>18.0</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>127</v>
+      <c r="D19" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
+      <c r="K19" s="12">
+        <v>4.0</v>
+      </c>
       <c r="L19" s="15"/>
-      <c r="M19" s="10"/>
+      <c r="M19" s="12">
+        <v>4.0</v>
+      </c>
       <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
+      <c r="O19" s="12">
+        <v>4.0</v>
+      </c>
       <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
+      <c r="Q19" s="12">
+        <v>3.0</v>
+      </c>
       <c r="R19" s="10"/>
-      <c r="S19" s="16"/>
+      <c r="S19" s="19">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="20" ht="126.75" customHeight="1">
       <c r="A20" s="10" t="s">
@@ -5260,19 +5475,19 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="F20" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="H20" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>25</v>
@@ -6376,19 +6591,19 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>136</v>
-      </c>
       <c r="H2" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>25</v>
@@ -6421,31 +6636,41 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="K3" s="24">
+        <v>4.0</v>
+      </c>
       <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
+      <c r="M3" s="24">
+        <v>4.0</v>
+      </c>
       <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
+      <c r="O3" s="24">
+        <v>5.0</v>
+      </c>
       <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
+      <c r="Q3" s="24">
+        <v>5.0</v>
+      </c>
       <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
+      <c r="S3" s="24">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="4" ht="126.75" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -6456,20 +6681,20 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -7507,7 +7732,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
@@ -7581,19 +7806,19 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>146</v>
-      </c>
       <c r="H2" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I2" s="16" t="s">
         <v>25</v>
@@ -7602,7 +7827,7 @@
       <c r="K2" s="19">
         <v>3.0</v>
       </c>
-      <c r="L2" s="20"/>
+      <c r="L2" s="25"/>
       <c r="M2" s="19">
         <v>2.0</v>
       </c>
@@ -7626,31 +7851,41 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H3" s="18" t="s">
         <v>45</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="18"/>
+      <c r="K3" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="L3" s="26"/>
+      <c r="M3" s="24">
+        <v>4.0</v>
+      </c>
       <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
+      <c r="O3" s="24">
+        <v>4.0</v>
+      </c>
       <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
+      <c r="Q3" s="24">
+        <v>3.0</v>
+      </c>
       <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
+      <c r="S3" s="24">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="4" ht="126.75" customHeight="1">
       <c r="A4" s="16" t="s">
@@ -7661,24 +7896,24 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="22" t="s">
-        <v>151</v>
+      <c r="I4" s="27" t="s">
+        <v>150</v>
       </c>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
-      <c r="L4" s="20"/>
+      <c r="L4" s="25"/>
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
       <c r="O4" s="16"/>
@@ -7696,33 +7931,43 @@
         <v>5.0</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>152</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>153</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>45</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="16"/>
+      <c r="K5" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="L5" s="25"/>
+      <c r="M5" s="19">
+        <v>5.0</v>
+      </c>
       <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
+      <c r="O5" s="19">
+        <v>4.0</v>
+      </c>
       <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
+      <c r="Q5" s="19">
+        <v>4.0</v>
+      </c>
       <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
+      <c r="S5" s="19">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="6" ht="126.75" customHeight="1">
       <c r="A6" s="16" t="s">
@@ -7733,24 +7978,24 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="22" t="s">
-        <v>155</v>
+      <c r="I6" s="27" t="s">
+        <v>154</v>
       </c>
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
-      <c r="L6" s="20"/>
+      <c r="L6" s="25"/>
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
@@ -7768,33 +8013,43 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>156</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>157</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>45</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="16"/>
+      <c r="K7" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="L7" s="25"/>
+      <c r="M7" s="19">
+        <v>4.0</v>
+      </c>
       <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
+      <c r="O7" s="19">
+        <v>3.0</v>
+      </c>
       <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
+      <c r="Q7" s="19">
+        <v>4.0</v>
+      </c>
       <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
+      <c r="S7" s="19">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="8" ht="126.75" customHeight="1">
       <c r="A8" s="18" t="s">
@@ -7805,24 +8060,24 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H8" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="23" t="s">
-        <v>160</v>
+      <c r="I8" s="28" t="s">
+        <v>159</v>
       </c>
       <c r="J8" s="18"/>
       <c r="K8" s="18"/>
-      <c r="L8" s="21"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="18"/>
       <c r="N8" s="18"/>
       <c r="O8" s="18"/>
@@ -7842,31 +8097,39 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>163</v>
-      </c>
       <c r="H9" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="16"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="L9" s="25"/>
+      <c r="M9" s="19">
+        <v>3.0</v>
+      </c>
       <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
+      <c r="O9" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19">
+        <v>3.0</v>
+      </c>
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
     </row>
